--- a/data/supplementary_tables/Supplementary Table 4.xlsx
+++ b/data/supplementary_tables/Supplementary Table 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFC31FC-9001-7741-A7BB-2D8695569C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD1F167-CA33-2346-837C-316758A136A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7360" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="2504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6046" uniqueCount="2508">
   <si>
     <t>genome_name</t>
   </si>
@@ -7532,6 +7532,18 @@
   </si>
   <si>
     <t>Supplementary Table 4 | Genome accessions and GTDB taxonomic classification of archaeal, bacterial and eukaryotic genomes in dataset GS-Liu2021-B</t>
+  </si>
+  <si>
+    <t>Rhodocyclales</t>
+  </si>
+  <si>
+    <t>Azonexaceae</t>
+  </si>
+  <si>
+    <t>Dechloromonas</t>
+  </si>
+  <si>
+    <t>Dechloromonas aromatica</t>
   </si>
 </sst>
 </file>
@@ -25360,6 +25372,24 @@
       <c r="B671" s="1" t="s">
         <v>749</v>
       </c>
+      <c r="C671" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>2504</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="G671" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="H671" s="1" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A672" s="1" t="s">
